--- a/PKSim/Analog9_PKSim.xlsx
+++ b/PKSim/Analog9_PKSim.xlsx
@@ -6,7 +6,7 @@
     <workbookView tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="Analog9_PKSim" sheetId="1" r:id="rId3"/>
+    <sheet name="Analog10_PKSim" sheetId="1" r:id="rId3"/>
     <sheet name="Global PK-Analyses" sheetId="2" r:id="rId4"/>
     <sheet name="PK-Analyses" sheetId="3" r:id="rId5"/>
   </sheets>
@@ -19,16 +19,16 @@
     <t xml:space="preserve">Time [h]</t>
   </si>
   <si>
-    <t xml:space="preserve">Analog1_Human_IVBolus_0p01mg-Peripheral Venous Blood-Plasma-Concentration [µmol/l]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog1_Human_IVBolus_0p01mg-Arterial Blood-Plasma-Concentration [µmol/l]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog1_Human_IVBolus_0p01mg-Brain-Tissue-Concentration [µmol/l]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog1_Human_IVBolus_0p01mg-Liver-Tissue-Concentration [µmol/l]</t>
+    <t xml:space="preserve">Analog10-Peripheral Venous Blood-Plasma-Concentration [µmol/l]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog10-Arterial Blood-Plasma-Concentration [µmol/l]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog10-Brain-Tissue-Concentration [µmol/l]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog10-Liver-Tissue-Concentration [µmol/l]</t>
   </si>
   <si>
     <t xml:space="preserve">Parameter</t>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Vss (plasma)</t>
   </si>
   <si>
-    <t xml:space="preserve">Analog1_Human_IVBolus_0p01mg</t>
+    <t xml:space="preserve">Analog10</t>
   </si>
   <si>
     <t xml:space="preserve">ml/kg</t>
@@ -64,16 +64,16 @@
     <t xml:space="preserve">Vss (phys-chem)</t>
   </si>
   <si>
-    <t xml:space="preserve">Analog1_Human_IVBolus_0p01mg - Analog1_Human_IVBolus_0p01mg-Arterial Blood-Plasma-Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog1_Human_IVBolus_0p01mg - Analog1_Human_IVBolus_0p01mg-Brain-Tissue-Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog1_Human_IVBolus_0p01mg - Analog1_Human_IVBolus_0p01mg-Liver-Tissue-Concentration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog1_Human_IVBolus_0p01mg - Analog1_Human_IVBolus_0p01mg-Peripheral Venous Blood-Plasma-Concentration</t>
+    <t xml:space="preserve">Analog10 - Analog10-Arterial Blood-Plasma-Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog10 - Analog10-Brain-Tissue-Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog10 - Analog10-Liver-Tissue-Concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog10 - Analog10-Peripheral Venous Blood-Plasma-Concentration</t>
   </si>
   <si>
     <t xml:space="preserve">AUC_inf [µmol*min/l]</t>
@@ -173,10 +173,10 @@
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.55" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="90.3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="79.2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="70.2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="69.9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="65.1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.85" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -218,16 +218,16 @@
         <v>0.05</v>
       </c>
       <c r="B3" s="2">
-        <v>0.001532672</v>
+        <v>0.001490698</v>
       </c>
       <c r="C3" s="2">
-        <v>0.001203982</v>
+        <v>0.001166836</v>
       </c>
       <c r="D3" s="2">
-        <v>3.178826E-06</v>
+        <v>3.05737E-06</v>
       </c>
       <c r="E3" s="2">
-        <v>0.001567156</v>
+        <v>0.001506795</v>
       </c>
     </row>
     <row r="4">
@@ -235,16 +235,16 @@
         <v>0.1</v>
       </c>
       <c r="B4" s="2">
-        <v>0.001056147</v>
+        <v>0.001021768</v>
       </c>
       <c r="C4" s="2">
-        <v>0.0008904242</v>
+        <v>0.0008470261</v>
       </c>
       <c r="D4" s="2">
-        <v>2.435702E-06</v>
+        <v>2.242899E-06</v>
       </c>
       <c r="E4" s="2">
-        <v>0.001938311</v>
+        <v>0.001916331</v>
       </c>
     </row>
     <row r="5">
@@ -252,16 +252,16 @@
         <v>0.15</v>
       </c>
       <c r="B5" s="2">
-        <v>0.0008294077</v>
+        <v>0.0007927016</v>
       </c>
       <c r="C5" s="2">
-        <v>0.0007787196</v>
+        <v>0.0007369178</v>
       </c>
       <c r="D5" s="2">
-        <v>2.428792E-06</v>
+        <v>2.198494E-06</v>
       </c>
       <c r="E5" s="2">
-        <v>0.001858289</v>
+        <v>0.001882438</v>
       </c>
     </row>
     <row r="6">
@@ -269,16 +269,16 @@
         <v>0.2</v>
       </c>
       <c r="B6" s="2">
-        <v>0.0007124708</v>
+        <v>0.0006770687</v>
       </c>
       <c r="C6" s="2">
-        <v>0.000697803</v>
+        <v>0.0006623933</v>
       </c>
       <c r="D6" s="2">
-        <v>2.477995E-06</v>
+        <v>2.229961E-06</v>
       </c>
       <c r="E6" s="2">
-        <v>0.001675418</v>
+        <v>0.001726393</v>
       </c>
     </row>
     <row r="7">
@@ -286,16 +286,16 @@
         <v>0.25</v>
       </c>
       <c r="B7" s="2">
-        <v>0.000637418</v>
+        <v>0.0006055182</v>
       </c>
       <c r="C7" s="2">
-        <v>0.0006308057</v>
+        <v>0.0006015059</v>
       </c>
       <c r="D7" s="2">
-        <v>2.533986E-06</v>
+        <v>2.272882E-06</v>
       </c>
       <c r="E7" s="2">
-        <v>0.001491578</v>
+        <v>0.001554366</v>
       </c>
     </row>
     <row r="8">
@@ -303,16 +303,16 @@
         <v>0.3</v>
       </c>
       <c r="B8" s="2">
-        <v>0.0005810342</v>
+        <v>0.0005527959</v>
       </c>
       <c r="C8" s="2">
-        <v>0.0005743337</v>
+        <v>0.0005497456</v>
       </c>
       <c r="D8" s="2">
-        <v>2.591737E-06</v>
+        <v>2.318422E-06</v>
       </c>
       <c r="E8" s="2">
-        <v>0.001330815</v>
+        <v>0.001397106</v>
       </c>
     </row>
     <row r="9">
@@ -320,16 +320,16 @@
         <v>0.35</v>
       </c>
       <c r="B9" s="2">
-        <v>0.0005352905</v>
+        <v>0.0005100867</v>
       </c>
       <c r="C9" s="2">
-        <v>0.0005265953</v>
+        <v>0.000505394</v>
       </c>
       <c r="D9" s="2">
-        <v>2.650525E-06</v>
+        <v>2.365059E-06</v>
       </c>
       <c r="E9" s="2">
-        <v>0.001195338</v>
+        <v>0.001260966</v>
       </c>
     </row>
     <row r="10">
@@ -337,16 +337,16 @@
         <v>0.4</v>
       </c>
       <c r="B10" s="2">
-        <v>0.0004969309</v>
+        <v>0.0004740388</v>
       </c>
       <c r="C10" s="2">
-        <v>0.0004861127</v>
+        <v>0.0004672848</v>
       </c>
       <c r="D10" s="2">
-        <v>2.709979E-06</v>
+        <v>2.412369E-06</v>
       </c>
       <c r="E10" s="2">
-        <v>0.001081997</v>
+        <v>0.001144932</v>
       </c>
     </row>
     <row r="11">
@@ -354,16 +354,16 @@
         <v>0.45</v>
       </c>
       <c r="B11" s="2">
-        <v>0.0004642789</v>
+        <v>0.0004430895</v>
       </c>
       <c r="C11" s="2">
-        <v>0.0004516181</v>
+        <v>0.0004344338</v>
       </c>
       <c r="D11" s="2">
-        <v>2.769732E-06</v>
+        <v>2.460089E-06</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0009869077</v>
+        <v>0.001046186</v>
       </c>
     </row>
     <row r="12">
@@ -371,16 +371,16 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="2">
-        <v>0.0004362065</v>
+        <v>0.0004162352</v>
       </c>
       <c r="C12" s="2">
-        <v>0.0004220555</v>
+        <v>0.0004059958</v>
       </c>
       <c r="D12" s="2">
-        <v>2.829451E-06</v>
+        <v>2.507962E-06</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0009066986</v>
+        <v>0.0009619453</v>
       </c>
     </row>
     <row r="13">
@@ -388,16 +388,16 @@
         <v>0.55</v>
       </c>
       <c r="B13" s="2">
-        <v>0.0004118804</v>
+        <v>0.000392797</v>
       </c>
       <c r="C13" s="2">
-        <v>0.0003965632</v>
+        <v>0.000381267</v>
       </c>
       <c r="D13" s="2">
-        <v>2.888872E-06</v>
+        <v>2.555782E-06</v>
       </c>
       <c r="E13" s="2">
-        <v>0.0008386162</v>
+        <v>0.0008897172</v>
       </c>
     </row>
     <row r="14">
@@ -405,16 +405,16 @@
         <v>0.6</v>
       </c>
       <c r="B14" s="2">
-        <v>0.0003906376</v>
+        <v>0.0003722282</v>
       </c>
       <c r="C14" s="2">
-        <v>0.0003744411</v>
+        <v>0.0003596577</v>
       </c>
       <c r="D14" s="2">
-        <v>2.947792E-06</v>
+        <v>2.603378E-06</v>
       </c>
       <c r="E14" s="2">
-        <v>0.0007804742</v>
+        <v>0.0008274584</v>
       </c>
     </row>
     <row r="15">
@@ -422,16 +422,16 @@
         <v>0.65</v>
       </c>
       <c r="B15" s="2">
-        <v>0.000371956</v>
+        <v>0.0003540632</v>
       </c>
       <c r="C15" s="2">
-        <v>0.0003551231</v>
+        <v>0.0003406793</v>
       </c>
       <c r="D15" s="2">
-        <v>3.006072E-06</v>
+        <v>2.650615E-06</v>
       </c>
       <c r="E15" s="2">
-        <v>0.0007305095</v>
+        <v>0.0007735373</v>
       </c>
     </row>
     <row r="16">
@@ -439,16 +439,16 @@
         <v>0.7</v>
       </c>
       <c r="B16" s="2">
-        <v>0.0003554164</v>
+        <v>0.0003379337</v>
       </c>
       <c r="C16" s="2">
-        <v>0.0003381475</v>
+        <v>0.0003239288</v>
       </c>
       <c r="D16" s="2">
-        <v>3.063609E-06</v>
+        <v>2.697396E-06</v>
       </c>
       <c r="E16" s="2">
-        <v>0.0006873045</v>
+        <v>0.0007266007</v>
       </c>
     </row>
     <row r="17">
@@ -456,16 +456,16 @@
         <v>0.75</v>
       </c>
       <c r="B17" s="2">
-        <v>0.0003406727</v>
+        <v>0.0003235337</v>
       </c>
       <c r="C17" s="2">
-        <v>0.0003231357</v>
+        <v>0.00030907</v>
       </c>
       <c r="D17" s="2">
-        <v>3.120329E-06</v>
+        <v>2.74365E-06</v>
       </c>
       <c r="E17" s="2">
-        <v>0.000649722</v>
+        <v>0.0006855403</v>
       </c>
     </row>
     <row r="18">
@@ -473,16 +473,16 @@
         <v>0.8</v>
       </c>
       <c r="B18" s="2">
-        <v>0.0003274398</v>
+        <v>0.0003106082</v>
       </c>
       <c r="C18" s="2">
-        <v>0.0003097766</v>
+        <v>0.0002958236</v>
       </c>
       <c r="D18" s="2">
-        <v>3.176183E-06</v>
+        <v>2.789324E-06</v>
       </c>
       <c r="E18" s="2">
-        <v>0.0006168358</v>
+        <v>0.0006494488</v>
       </c>
     </row>
     <row r="19">
@@ -490,16 +490,16 @@
         <v>0.85</v>
       </c>
       <c r="B19" s="2">
-        <v>0.0003154855</v>
+        <v>0.0002989435</v>
       </c>
       <c r="C19" s="2">
-        <v>0.0002978134</v>
+        <v>0.000283956</v>
       </c>
       <c r="D19" s="2">
-        <v>3.231139E-06</v>
+        <v>2.83438E-06</v>
       </c>
       <c r="E19" s="2">
-        <v>0.0005878819</v>
+        <v>0.0006175757</v>
       </c>
     </row>
     <row r="20">
@@ -507,16 +507,16 @@
         <v>0.9</v>
       </c>
       <c r="B20" s="2">
-        <v>0.0003046214</v>
+        <v>0.0002883617</v>
       </c>
       <c r="C20" s="2">
-        <v>0.0002870344</v>
+        <v>0.0002732709</v>
       </c>
       <c r="D20" s="2">
-        <v>3.285178E-06</v>
+        <v>2.878794E-06</v>
       </c>
       <c r="E20" s="2">
-        <v>0.0005622293</v>
+        <v>0.0005892934</v>
       </c>
     </row>
     <row r="21">
@@ -524,16 +524,16 @@
         <v>0.95</v>
       </c>
       <c r="B21" s="2">
-        <v>0.0002946913</v>
+        <v>0.0002787136</v>
       </c>
       <c r="C21" s="2">
-        <v>0.0002772641</v>
+        <v>0.0002636027</v>
       </c>
       <c r="D21" s="2">
-        <v>3.338292E-06</v>
+        <v>2.92255E-06</v>
       </c>
       <c r="E21" s="2">
-        <v>0.0005393604</v>
+        <v>0.0005640741</v>
       </c>
     </row>
     <row r="22">
@@ -541,16 +541,16 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>0.0002855644</v>
+        <v>0.0002698737</v>
       </c>
       <c r="C22" s="2">
-        <v>0.0002683566</v>
+        <v>0.0002548113</v>
       </c>
       <c r="D22" s="2">
-        <v>3.39048E-06</v>
+        <v>2.965638E-06</v>
       </c>
       <c r="E22" s="2">
-        <v>0.0005188507</v>
+        <v>0.0005414751</v>
       </c>
     </row>
     <row r="23">
@@ -558,16 +558,16 @@
         <v>1.05</v>
       </c>
       <c r="B23" s="2">
-        <v>0.0002771312</v>
+        <v>0.0002617359</v>
       </c>
       <c r="C23" s="2">
-        <v>0.0002601906</v>
+        <v>0.0002467787</v>
       </c>
       <c r="D23" s="2">
-        <v>3.441745E-06</v>
+        <v>3.008052E-06</v>
       </c>
       <c r="E23" s="2">
-        <v>0.0005003482</v>
+        <v>0.000521125</v>
       </c>
     </row>
     <row r="24">
@@ -575,16 +575,16 @@
         <v>1.1</v>
       </c>
       <c r="B24" s="2">
-        <v>0.0002692992</v>
+        <v>0.0002542096</v>
       </c>
       <c r="C24" s="2">
-        <v>0.000252664</v>
+        <v>0.0002394043</v>
       </c>
       <c r="D24" s="2">
-        <v>3.492094E-06</v>
+        <v>3.049794E-06</v>
       </c>
       <c r="E24" s="2">
-        <v>0.0004835598</v>
+        <v>0.0005027093</v>
       </c>
     </row>
     <row r="25">
@@ -592,16 +592,16 @@
         <v>1.15</v>
       </c>
       <c r="B25" s="2">
-        <v>0.0002619903</v>
+        <v>0.0002472186</v>
       </c>
       <c r="C25" s="2">
-        <v>0.0002456907</v>
+        <v>0.0002326031</v>
       </c>
       <c r="D25" s="2">
-        <v>3.54154E-06</v>
+        <v>3.090866E-06</v>
       </c>
       <c r="E25" s="2">
-        <v>0.0004682363</v>
+        <v>0.0004859632</v>
       </c>
     </row>
     <row r="26">
@@ -609,16 +609,16 @@
         <v>1.2</v>
       </c>
       <c r="B26" s="2">
-        <v>0.0002551418</v>
+        <v>0.0002406977</v>
       </c>
       <c r="C26" s="2">
-        <v>0.0002391998</v>
+        <v>0.0002263025</v>
       </c>
       <c r="D26" s="2">
-        <v>3.590096E-06</v>
+        <v>3.131274E-06</v>
       </c>
       <c r="E26" s="2">
-        <v>0.0004541729</v>
+        <v>0.000470661</v>
       </c>
     </row>
     <row r="27">
@@ -626,16 +626,16 @@
         <v>1.25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.0002486981</v>
+        <v>0.0002345926</v>
       </c>
       <c r="C27" s="2">
-        <v>0.0002331296</v>
+        <v>0.0002204421</v>
       </c>
       <c r="D27" s="2">
-        <v>3.637778E-06</v>
+        <v>3.171025E-06</v>
       </c>
       <c r="E27" s="2">
-        <v>0.0004411925</v>
+        <v>0.0004566161</v>
       </c>
     </row>
     <row r="28">
@@ -643,16 +643,16 @@
         <v>1.3</v>
       </c>
       <c r="B28" s="2">
-        <v>0.0002426151</v>
+        <v>0.000228856</v>
       </c>
       <c r="C28" s="2">
-        <v>0.0002274304</v>
+        <v>0.0002149694</v>
       </c>
       <c r="D28" s="2">
-        <v>3.684603E-06</v>
+        <v>3.210128E-06</v>
       </c>
       <c r="E28" s="2">
-        <v>0.0004291526</v>
+        <v>0.000443667</v>
       </c>
     </row>
     <row r="29">
@@ -660,16 +660,16 @@
         <v>1.35</v>
       </c>
       <c r="B29" s="2">
-        <v>0.0002368543</v>
+        <v>0.0002234474</v>
       </c>
       <c r="C29" s="2">
-        <v>0.0002220597</v>
+        <v>0.0002098393</v>
       </c>
       <c r="D29" s="2">
-        <v>3.730591E-06</v>
+        <v>3.248595E-06</v>
       </c>
       <c r="E29" s="2">
-        <v>0.0004179335</v>
+        <v>0.0004316752</v>
       </c>
     </row>
     <row r="30">
@@ -677,16 +677,16 @@
         <v>1.4</v>
       </c>
       <c r="B30" s="2">
-        <v>0.0002313831</v>
+        <v>0.0002183318</v>
       </c>
       <c r="C30" s="2">
-        <v>0.0002169817</v>
+        <v>0.0002050132</v>
       </c>
       <c r="D30" s="2">
-        <v>3.77576E-06</v>
+        <v>3.286435E-06</v>
       </c>
       <c r="E30" s="2">
-        <v>0.0004074352</v>
+        <v>0.0004205227</v>
       </c>
     </row>
     <row r="31">
@@ -694,16 +694,16 @@
         <v>1.45</v>
       </c>
       <c r="B31" s="2">
-        <v>0.0002261733</v>
+        <v>0.0002134788</v>
       </c>
       <c r="C31" s="2">
-        <v>0.0002121659</v>
+        <v>0.0002004574</v>
       </c>
       <c r="D31" s="2">
-        <v>3.82013E-06</v>
+        <v>3.323662E-06</v>
       </c>
       <c r="E31" s="2">
-        <v>0.0003975731</v>
+        <v>0.000410107</v>
       </c>
     </row>
     <row r="32">
@@ -711,16 +711,16 @@
         <v>1.5</v>
       </c>
       <c r="B32" s="2">
-        <v>0.0002212011</v>
+        <v>0.0002088628</v>
       </c>
       <c r="C32" s="2">
-        <v>0.0002075865</v>
+        <v>0.0001961437</v>
       </c>
       <c r="D32" s="2">
-        <v>3.863721E-06</v>
+        <v>3.360287E-06</v>
       </c>
       <c r="E32" s="2">
-        <v>0.0003882753</v>
+        <v>0.0004003425</v>
       </c>
     </row>
     <row r="33">
@@ -728,16 +728,16 @@
         <v>1.55</v>
       </c>
       <c r="B33" s="2">
-        <v>0.0002164456</v>
+        <v>0.0002044616</v>
       </c>
       <c r="C33" s="2">
-        <v>0.0002032208</v>
+        <v>0.0001920477</v>
       </c>
       <c r="D33" s="2">
-        <v>3.906553E-06</v>
+        <v>3.396322E-06</v>
       </c>
       <c r="E33" s="2">
-        <v>0.000379479</v>
+        <v>0.0003911559</v>
       </c>
     </row>
     <row r="34">
@@ -745,16 +745,16 @@
         <v>1.6</v>
       </c>
       <c r="B34" s="2">
-        <v>0.0002118895</v>
+        <v>0.0002002562</v>
       </c>
       <c r="C34" s="2">
-        <v>0.0001990498</v>
+        <v>0.0001881487</v>
       </c>
       <c r="D34" s="2">
-        <v>3.948645E-06</v>
+        <v>3.431782E-06</v>
       </c>
       <c r="E34" s="2">
-        <v>0.0003711322</v>
+        <v>0.0003824849</v>
       </c>
     </row>
     <row r="35">
@@ -762,16 +762,16 @@
         <v>1.65</v>
       </c>
       <c r="B35" s="2">
-        <v>0.0002075175</v>
+        <v>0.0001962301</v>
       </c>
       <c r="C35" s="2">
-        <v>0.000195057</v>
+        <v>0.0001844284</v>
       </c>
       <c r="D35" s="2">
-        <v>3.990018E-06</v>
+        <v>3.466679E-06</v>
       </c>
       <c r="E35" s="2">
-        <v>0.0003631899</v>
+        <v>0.0003742759</v>
       </c>
     </row>
     <row r="36">
@@ -779,16 +779,16 @@
         <v>1.7</v>
       </c>
       <c r="B36" s="2">
-        <v>0.0002033162</v>
+        <v>0.000192369</v>
       </c>
       <c r="C36" s="2">
-        <v>0.0001912283</v>
+        <v>0.0001808717</v>
       </c>
       <c r="D36" s="2">
-        <v>4.030691E-06</v>
+        <v>3.501026E-06</v>
       </c>
       <c r="E36" s="2">
-        <v>0.0003556148</v>
+        <v>0.0003664837</v>
       </c>
     </row>
     <row r="37">
@@ -796,16 +796,16 @@
         <v>1.75</v>
       </c>
       <c r="B37" s="2">
-        <v>0.0001992742</v>
+        <v>0.0001886602</v>
       </c>
       <c r="C37" s="2">
-        <v>0.0001875515</v>
+        <v>0.0001774646</v>
       </c>
       <c r="D37" s="2">
-        <v>4.070684E-06</v>
+        <v>3.534837E-06</v>
       </c>
       <c r="E37" s="2">
-        <v>0.0003483748</v>
+        <v>0.0003590673</v>
       </c>
     </row>
     <row r="38">
@@ -813,16 +813,16 @@
         <v>1.8</v>
       </c>
       <c r="B38" s="2">
-        <v>0.0001953811</v>
+        <v>0.0001850927</v>
       </c>
       <c r="C38" s="2">
-        <v>0.000184016</v>
+        <v>0.0001741953</v>
       </c>
       <c r="D38" s="2">
-        <v>4.110015E-06</v>
+        <v>3.568125E-06</v>
       </c>
       <c r="E38" s="2">
-        <v>0.0003414426</v>
+        <v>0.0003519925</v>
       </c>
     </row>
     <row r="39">
@@ -830,16 +830,16 @@
         <v>1.85</v>
       </c>
       <c r="B39" s="2">
-        <v>0.000191628</v>
+        <v>0.0001816569</v>
       </c>
       <c r="C39" s="2">
-        <v>0.0001806126</v>
+        <v>0.0001710537</v>
       </c>
       <c r="D39" s="2">
-        <v>4.148704E-06</v>
+        <v>3.600903E-06</v>
       </c>
       <c r="E39" s="2">
-        <v>0.0003347938</v>
+        <v>0.00034523</v>
       </c>
     </row>
     <row r="40">
@@ -847,16 +847,16 @@
         <v>1.9</v>
       </c>
       <c r="B40" s="2">
-        <v>0.000188007</v>
+        <v>0.0001783431</v>
       </c>
       <c r="C40" s="2">
-        <v>0.0001773328</v>
+        <v>0.0001680292</v>
       </c>
       <c r="D40" s="2">
-        <v>4.186768E-06</v>
+        <v>3.633183E-06</v>
       </c>
       <c r="E40" s="2">
-        <v>0.0003284074</v>
+        <v>0.0003387495</v>
       </c>
     </row>
     <row r="41">
@@ -864,16 +864,16 @@
         <v>1.95</v>
       </c>
       <c r="B41" s="2">
-        <v>0.0001845109</v>
+        <v>0.0001751451</v>
       </c>
       <c r="C41" s="2">
-        <v>0.0001741696</v>
+        <v>0.0001651155</v>
       </c>
       <c r="D41" s="2">
-        <v>4.224227E-06</v>
+        <v>3.664978E-06</v>
       </c>
       <c r="E41" s="2">
-        <v>0.0003222653</v>
+        <v>0.0003325331</v>
       </c>
     </row>
     <row r="42">
@@ -881,16 +881,16 @@
         <v>2</v>
       </c>
       <c r="B42" s="2">
-        <v>0.0001811336</v>
+        <v>0.0001720547</v>
       </c>
       <c r="C42" s="2">
-        <v>0.0001711165</v>
+        <v>0.000162304</v>
       </c>
       <c r="D42" s="2">
-        <v>4.261096E-06</v>
+        <v>3.696301E-06</v>
       </c>
       <c r="E42" s="2">
-        <v>0.0003163516</v>
+        <v>0.0003265563</v>
       </c>
     </row>
     <row r="43">
@@ -898,16 +898,16 @@
         <v>2.25</v>
       </c>
       <c r="B43" s="2">
-        <v>0.0001658404</v>
+        <v>0.0001580326</v>
       </c>
       <c r="C43" s="2">
-        <v>0.0001573155</v>
+        <v>0.0001495877</v>
       </c>
       <c r="D43" s="2">
-        <v>4.43719E-06</v>
+        <v>3.846245E-06</v>
       </c>
       <c r="E43" s="2">
-        <v>0.000289762</v>
+        <v>0.0002997474</v>
       </c>
     </row>
     <row r="44">
@@ -915,16 +915,16 @@
         <v>2.5</v>
       </c>
       <c r="B44" s="2">
-        <v>0.0001528216</v>
+        <v>0.000146025</v>
       </c>
       <c r="C44" s="2">
-        <v>0.0001455847</v>
+        <v>0.000138735</v>
       </c>
       <c r="D44" s="2">
-        <v>4.600937E-06</v>
+        <v>3.986108E-06</v>
       </c>
       <c r="E44" s="2">
-        <v>0.0002672871</v>
+        <v>0.0002770848</v>
       </c>
     </row>
     <row r="45">
@@ -932,16 +932,16 @@
         <v>2.75</v>
       </c>
       <c r="B45" s="2">
-        <v>0.0001416865</v>
+        <v>0.0001356632</v>
       </c>
       <c r="C45" s="2">
-        <v>0.0001355552</v>
+        <v>0.000129384</v>
       </c>
       <c r="D45" s="2">
-        <v>4.754046E-06</v>
+        <v>4.117162E-06</v>
       </c>
       <c r="E45" s="2">
-        <v>0.0002481292</v>
+        <v>0.0002576614</v>
       </c>
     </row>
     <row r="46">
@@ -949,16 +949,16 @@
         <v>3</v>
       </c>
       <c r="B46" s="2">
-        <v>0.0001321385</v>
+        <v>0.0001266778</v>
       </c>
       <c r="C46" s="2">
-        <v>0.0001269533</v>
+        <v>0.0001212781</v>
       </c>
       <c r="D46" s="2">
-        <v>4.897988E-06</v>
+        <v>4.240524E-06</v>
       </c>
       <c r="E46" s="2">
-        <v>0.0002317289</v>
+        <v>0.0002408689</v>
       </c>
     </row>
     <row r="47">
@@ -966,16 +966,16 @@
         <v>3.25</v>
       </c>
       <c r="B47" s="2">
-        <v>0.0001239295</v>
+        <v>0.0001188644</v>
       </c>
       <c r="C47" s="2">
-        <v>0.000119552</v>
+        <v>0.0001142274</v>
       </c>
       <c r="D47" s="2">
-        <v>5.034024E-06</v>
+        <v>4.357169E-06</v>
       </c>
       <c r="E47" s="2">
-        <v>0.0002176279</v>
+        <v>0.0002262826</v>
       </c>
     </row>
     <row r="48">
@@ -983,16 +983,16 @@
         <v>3.5</v>
       </c>
       <c r="B48" s="2">
-        <v>0.0001168637</v>
+        <v>0.0001120629</v>
       </c>
       <c r="C48" s="2">
-        <v>0.0001131754</v>
+        <v>0.0001080871</v>
       </c>
       <c r="D48" s="2">
-        <v>5.163234E-06</v>
+        <v>4.467946E-06</v>
       </c>
       <c r="E48" s="2">
-        <v>0.0002054869</v>
+        <v>0.0002135951</v>
       </c>
     </row>
     <row r="49">
@@ -1000,16 +1000,16 @@
         <v>3.75</v>
       </c>
       <c r="B49" s="2">
-        <v>0.0001107788</v>
+        <v>0.0001061343</v>
       </c>
       <c r="C49" s="2">
-        <v>0.0001076788</v>
+        <v>0.0001027313</v>
       </c>
       <c r="D49" s="2">
-        <v>5.286544E-06</v>
+        <v>4.573591E-06</v>
       </c>
       <c r="E49" s="2">
-        <v>0.0001950331</v>
+        <v>0.0002025386</v>
       </c>
     </row>
     <row r="50">
@@ -1017,16 +1017,16 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>0.0001055303</v>
+        <v>0.0001009591</v>
       </c>
       <c r="C50" s="2">
-        <v>0.0001029322</v>
+        <v>9.805156E-05</v>
       </c>
       <c r="D50" s="2">
-        <v>5.404745E-06</v>
+        <v>4.674741E-06</v>
       </c>
       <c r="E50" s="2">
-        <v>0.0001860145</v>
+        <v>0.0001928839</v>
       </c>
     </row>
     <row r="51">
@@ -1034,16 +1034,16 @@
         <v>4.25</v>
       </c>
       <c r="B51" s="2">
-        <v>0.000100992</v>
+        <v>9.643698E-05</v>
       </c>
       <c r="C51" s="2">
-        <v>9.882137E-05</v>
+        <v>9.395825E-05</v>
       </c>
       <c r="D51" s="2">
-        <v>5.518513E-06</v>
+        <v>4.771952E-06</v>
       </c>
       <c r="E51" s="2">
-        <v>0.0001782063</v>
+        <v>0.0001844448</v>
       </c>
     </row>
     <row r="52">
@@ -1051,16 +1051,16 @@
         <v>4.5</v>
       </c>
       <c r="B52" s="2">
-        <v>9.706341E-05</v>
+        <v>9.248137E-05</v>
       </c>
       <c r="C52" s="2">
-        <v>9.525696E-05</v>
+        <v>9.037356E-05</v>
       </c>
       <c r="D52" s="2">
-        <v>5.628428E-06</v>
+        <v>4.865706E-06</v>
       </c>
       <c r="E52" s="2">
-        <v>0.0001714408</v>
+        <v>0.0001770601</v>
       </c>
     </row>
     <row r="53">
@@ -1068,16 +1068,16 @@
         <v>4.75</v>
       </c>
       <c r="B53" s="2">
-        <v>9.365943E-05</v>
+        <v>8.901636E-05</v>
       </c>
       <c r="C53" s="2">
-        <v>9.216347E-05</v>
+        <v>8.722932E-05</v>
       </c>
       <c r="D53" s="2">
-        <v>5.734987E-06</v>
+        <v>4.956418E-06</v>
       </c>
       <c r="E53" s="2">
-        <v>0.0001655769</v>
+        <v>0.0001705874</v>
       </c>
     </row>
     <row r="54">
@@ -1085,16 +1085,16 @@
         <v>5</v>
       </c>
       <c r="B54" s="2">
-        <v>9.070404E-05</v>
+        <v>8.597679E-05</v>
       </c>
       <c r="C54" s="2">
-        <v>8.947269E-05</v>
+        <v>8.446704E-05</v>
       </c>
       <c r="D54" s="2">
-        <v>5.838614E-06</v>
+        <v>5.044452E-06</v>
       </c>
       <c r="E54" s="2">
-        <v>0.0001604834</v>
+        <v>0.0001649055</v>
       </c>
     </row>
     <row r="55">
@@ -1102,16 +1102,16 @@
         <v>5.25</v>
       </c>
       <c r="B55" s="2">
-        <v>8.813104E-05</v>
+        <v>8.330628E-05</v>
       </c>
       <c r="C55" s="2">
-        <v>8.712489E-05</v>
+        <v>8.203621E-05</v>
       </c>
       <c r="D55" s="2">
-        <v>5.939675E-06</v>
+        <v>5.130124E-06</v>
       </c>
       <c r="E55" s="2">
-        <v>0.0001560441</v>
+        <v>0.0001599098</v>
       </c>
     </row>
     <row r="56">
@@ -1119,16 +1119,16 @@
         <v>5.5</v>
       </c>
       <c r="B56" s="2">
-        <v>8.588524E-05</v>
+        <v>8.095604E-05</v>
       </c>
       <c r="C56" s="2">
-        <v>8.507059E-05</v>
+        <v>7.989311E-05</v>
       </c>
       <c r="D56" s="2">
-        <v>6.03848E-06</v>
+        <v>5.213706E-06</v>
       </c>
       <c r="E56" s="2">
-        <v>0.000152164</v>
+        <v>0.0001555097</v>
       </c>
     </row>
     <row r="57">
@@ -1136,16 +1136,16 @@
         <v>5.75</v>
       </c>
       <c r="B57" s="2">
-        <v>8.391963E-05</v>
+        <v>7.888434E-05</v>
       </c>
       <c r="C57" s="2">
-        <v>8.326769E-05</v>
+        <v>7.800041E-05</v>
       </c>
       <c r="D57" s="2">
-        <v>6.135298E-06</v>
+        <v>5.295436E-06</v>
       </c>
       <c r="E57" s="2">
-        <v>0.0001487625</v>
+        <v>0.0001516282</v>
       </c>
     </row>
     <row r="58">
@@ -1153,16 +1153,16 @@
         <v>6</v>
       </c>
       <c r="B58" s="2">
-        <v>8.219547E-05</v>
+        <v>7.705452E-05</v>
       </c>
       <c r="C58" s="2">
-        <v>8.168183E-05</v>
+        <v>7.632517E-05</v>
       </c>
       <c r="D58" s="2">
-        <v>6.230359E-06</v>
+        <v>5.375518E-06</v>
       </c>
       <c r="E58" s="2">
-        <v>0.0001457755</v>
+        <v>0.0001481969</v>
       </c>
     </row>
     <row r="59">
@@ -1170,16 +1170,16 @@
         <v>6.25</v>
       </c>
       <c r="B59" s="2">
-        <v>8.067846E-05</v>
+        <v>7.543475E-05</v>
       </c>
       <c r="C59" s="2">
-        <v>8.028227E-05</v>
+        <v>7.48388E-05</v>
       </c>
       <c r="D59" s="2">
-        <v>6.32386E-06</v>
+        <v>5.454132E-06</v>
       </c>
       <c r="E59" s="2">
-        <v>0.0001431443</v>
+        <v>0.0001451563</v>
       </c>
     </row>
     <row r="60">
@@ -1187,16 +1187,16 @@
         <v>6.5</v>
       </c>
       <c r="B60" s="2">
-        <v>7.933936E-05</v>
+        <v>7.399741E-05</v>
       </c>
       <c r="C60" s="2">
-        <v>7.904284E-05</v>
+        <v>7.351657E-05</v>
       </c>
       <c r="D60" s="2">
-        <v>6.415971E-06</v>
+        <v>5.531435E-06</v>
       </c>
       <c r="E60" s="2">
-        <v>0.0001408187</v>
+        <v>0.0001424552</v>
       </c>
     </row>
     <row r="61">
@@ -1204,16 +1204,16 @@
         <v>6.75</v>
       </c>
       <c r="B61" s="2">
-        <v>7.815327E-05</v>
+        <v>7.271879E-05</v>
       </c>
       <c r="C61" s="2">
-        <v>7.794132E-05</v>
+        <v>7.233716E-05</v>
       </c>
       <c r="D61" s="2">
-        <v>6.506838E-06</v>
+        <v>5.607562E-06</v>
       </c>
       <c r="E61" s="2">
-        <v>0.0001387568</v>
+        <v>0.0001400493</v>
       </c>
     </row>
     <row r="62">
@@ -1221,16 +1221,16 @@
         <v>7</v>
       </c>
       <c r="B62" s="2">
-        <v>7.709795E-05</v>
+        <v>7.157821E-05</v>
       </c>
       <c r="C62" s="2">
-        <v>7.695758E-05</v>
+        <v>7.128207E-05</v>
       </c>
       <c r="D62" s="2">
-        <v>6.596589E-06</v>
+        <v>5.682632E-06</v>
       </c>
       <c r="E62" s="2">
-        <v>0.0001369191</v>
+        <v>0.0001379003</v>
       </c>
     </row>
     <row r="63">
@@ -1238,16 +1238,16 @@
         <v>7.25</v>
       </c>
       <c r="B63" s="2">
-        <v>7.615498E-05</v>
+        <v>7.055778E-05</v>
       </c>
       <c r="C63" s="2">
-        <v>7.607508E-05</v>
+        <v>7.033526E-05</v>
       </c>
       <c r="D63" s="2">
-        <v>6.685329E-06</v>
+        <v>5.756747E-06</v>
       </c>
       <c r="E63" s="2">
-        <v>0.0001352737</v>
+        <v>0.0001359751</v>
       </c>
     </row>
     <row r="64">
@@ -1255,16 +1255,16 @@
         <v>7.5</v>
       </c>
       <c r="B64" s="2">
-        <v>7.530855E-05</v>
+        <v>6.964197E-05</v>
       </c>
       <c r="C64" s="2">
-        <v>7.527962E-05</v>
+        <v>6.948279E-05</v>
       </c>
       <c r="D64" s="2">
-        <v>6.773154E-06</v>
+        <v>5.829999E-06</v>
       </c>
       <c r="E64" s="2">
-        <v>0.0001337933</v>
+        <v>0.0001342449</v>
       </c>
     </row>
     <row r="65">
@@ -1272,16 +1272,16 @@
         <v>7.75</v>
       </c>
       <c r="B65" s="2">
-        <v>7.454569E-05</v>
+        <v>6.88174E-05</v>
       </c>
       <c r="C65" s="2">
-        <v>7.455965E-05</v>
+        <v>6.871267E-05</v>
       </c>
       <c r="D65" s="2">
-        <v>6.860144E-06</v>
+        <v>5.902466E-06</v>
       </c>
       <c r="E65" s="2">
-        <v>0.0001324563</v>
+        <v>0.0001326846</v>
       </c>
     </row>
     <row r="66">
@@ -1289,16 +1289,16 @@
         <v>8</v>
       </c>
       <c r="B66" s="2">
-        <v>7.385515E-05</v>
+        <v>6.807242E-05</v>
       </c>
       <c r="C66" s="2">
-        <v>7.390512E-05</v>
+        <v>6.801441E-05</v>
       </c>
       <c r="D66" s="2">
-        <v>6.946369E-06</v>
+        <v>5.974216E-06</v>
       </c>
       <c r="E66" s="2">
-        <v>0.0001312437</v>
+        <v>0.0001312728</v>
       </c>
     </row>
     <row r="67">
@@ -1306,16 +1306,16 @@
         <v>8.25</v>
       </c>
       <c r="B67" s="2">
-        <v>7.322732E-05</v>
+        <v>6.739688E-05</v>
       </c>
       <c r="C67" s="2">
-        <v>7.330748E-05</v>
+        <v>6.737896E-05</v>
       </c>
       <c r="D67" s="2">
-        <v>7.031891E-06</v>
+        <v>6.04531E-06</v>
       </c>
       <c r="E67" s="2">
-        <v>0.0001301393</v>
+        <v>0.0001299904</v>
       </c>
     </row>
     <row r="68">
@@ -1323,16 +1323,16 @@
         <v>8.5</v>
       </c>
       <c r="B68" s="2">
-        <v>7.265368E-05</v>
+        <v>6.678203E-05</v>
       </c>
       <c r="C68" s="2">
-        <v>7.275904E-05</v>
+        <v>6.679842E-05</v>
       </c>
       <c r="D68" s="2">
-        <v>7.11676E-06</v>
+        <v>6.1158E-06</v>
       </c>
       <c r="E68" s="2">
-        <v>0.0001291282</v>
+        <v>0.0001288212</v>
       </c>
     </row>
     <row r="69">
@@ -1340,16 +1340,16 @@
         <v>8.75</v>
       </c>
       <c r="B69" s="2">
-        <v>7.2127E-05</v>
+        <v>6.622017E-05</v>
       </c>
       <c r="C69" s="2">
-        <v>7.225331E-05</v>
+        <v>6.626589E-05</v>
       </c>
       <c r="D69" s="2">
-        <v>7.201024E-06</v>
+        <v>6.185733E-06</v>
       </c>
       <c r="E69" s="2">
-        <v>0.0001281981</v>
+        <v>0.000127751</v>
       </c>
     </row>
     <row r="70">
@@ -1357,16 +1357,16 @@
         <v>9</v>
       </c>
       <c r="B70" s="2">
-        <v>7.164098E-05</v>
+        <v>6.570479E-05</v>
       </c>
       <c r="C70" s="2">
-        <v>7.178459E-05</v>
+        <v>6.577554E-05</v>
       </c>
       <c r="D70" s="2">
-        <v>7.284724E-06</v>
+        <v>6.255149E-06</v>
       </c>
       <c r="E70" s="2">
-        <v>0.0001273378</v>
+        <v>0.0001267676</v>
       </c>
     </row>
     <row r="71">
@@ -1374,16 +1374,16 @@
         <v>9.25</v>
       </c>
       <c r="B71" s="2">
-        <v>7.119049E-05</v>
+        <v>6.523012E-05</v>
       </c>
       <c r="C71" s="2">
-        <v>7.134832E-05</v>
+        <v>6.532217E-05</v>
       </c>
       <c r="D71" s="2">
-        <v>7.367894E-06</v>
+        <v>6.324085E-06</v>
       </c>
       <c r="E71" s="2">
-        <v>0.0001265388</v>
+        <v>0.0001258603</v>
       </c>
     </row>
     <row r="72">
@@ -1391,16 +1391,16 @@
         <v>9.5</v>
       </c>
       <c r="B72" s="2">
-        <v>7.077106E-05</v>
+        <v>6.479127E-05</v>
       </c>
       <c r="C72" s="2">
-        <v>7.094048E-05</v>
+        <v>6.490142E-05</v>
       </c>
       <c r="D72" s="2">
-        <v>7.450565E-06</v>
+        <v>6.392572E-06</v>
       </c>
       <c r="E72" s="2">
-        <v>0.0001257934</v>
+        <v>0.0001250199</v>
       </c>
     </row>
     <row r="73">
@@ -1408,16 +1408,16 @@
         <v>9.75</v>
       </c>
       <c r="B73" s="2">
-        <v>7.037896E-05</v>
+        <v>6.43841E-05</v>
       </c>
       <c r="C73" s="2">
-        <v>7.055774E-05</v>
+        <v>6.450952E-05</v>
       </c>
       <c r="D73" s="2">
-        <v>7.532765E-06</v>
+        <v>6.460636E-06</v>
       </c>
       <c r="E73" s="2">
-        <v>0.0001250955</v>
+        <v>0.0001242389</v>
       </c>
     </row>
     <row r="74">
@@ -1425,16 +1425,16 @@
         <v>10</v>
       </c>
       <c r="B74" s="2">
-        <v>7.001084E-05</v>
+        <v>6.400477E-05</v>
       </c>
       <c r="C74" s="2">
-        <v>7.019709E-05</v>
+        <v>6.414306E-05</v>
       </c>
       <c r="D74" s="2">
-        <v>7.614517E-06</v>
+        <v>6.528302E-06</v>
       </c>
       <c r="E74" s="2">
-        <v>0.0001244391</v>
+        <v>0.00012351</v>
       </c>
     </row>
     <row r="75">
@@ -1442,16 +1442,16 @@
         <v>10.25</v>
       </c>
       <c r="B75" s="2">
-        <v>6.966382E-05</v>
+        <v>6.365019E-05</v>
       </c>
       <c r="C75" s="2">
-        <v>6.985595E-05</v>
+        <v>6.379925E-05</v>
       </c>
       <c r="D75" s="2">
-        <v>7.695843E-06</v>
+        <v>6.595593E-06</v>
       </c>
       <c r="E75" s="2">
-        <v>0.0001238194</v>
+        <v>0.0001228276</v>
       </c>
     </row>
     <row r="76">
@@ -1459,16 +1459,16 @@
         <v>10.5</v>
       </c>
       <c r="B76" s="2">
-        <v>6.933542E-05</v>
+        <v>6.331743E-05</v>
       </c>
       <c r="C76" s="2">
-        <v>6.953203E-05</v>
+        <v>6.347545E-05</v>
       </c>
       <c r="D76" s="2">
-        <v>7.776763E-06</v>
+        <v>6.662527E-06</v>
       </c>
       <c r="E76" s="2">
-        <v>0.000123232</v>
+        <v>0.000122186</v>
       </c>
     </row>
     <row r="77">
@@ -1476,16 +1476,16 @@
         <v>10.75</v>
       </c>
       <c r="B77" s="2">
-        <v>6.902355E-05</v>
+        <v>6.300398E-05</v>
       </c>
       <c r="C77" s="2">
-        <v>6.922348E-05</v>
+        <v>6.316941E-05</v>
       </c>
       <c r="D77" s="2">
-        <v>7.857292E-06</v>
+        <v>6.729122E-06</v>
       </c>
       <c r="E77" s="2">
-        <v>0.0001226733</v>
+        <v>0.0001215808</v>
       </c>
     </row>
     <row r="78">
@@ -1493,16 +1493,16 @@
         <v>11</v>
       </c>
       <c r="B78" s="2">
-        <v>6.872634E-05</v>
+        <v>6.270773E-05</v>
       </c>
       <c r="C78" s="2">
-        <v>6.892862E-05</v>
+        <v>6.287923E-05</v>
       </c>
       <c r="D78" s="2">
-        <v>7.937448E-06</v>
+        <v>6.795395E-06</v>
       </c>
       <c r="E78" s="2">
-        <v>0.0001221401</v>
+        <v>0.0001210079</v>
       </c>
     </row>
     <row r="79">
@@ -1510,16 +1510,16 @@
         <v>11.25</v>
       </c>
       <c r="B79" s="2">
-        <v>6.844231E-05</v>
+        <v>6.242668E-05</v>
       </c>
       <c r="C79" s="2">
-        <v>6.864613E-05</v>
+        <v>6.26031E-05</v>
       </c>
       <c r="D79" s="2">
-        <v>8.017243E-06</v>
+        <v>6.861359E-06</v>
       </c>
       <c r="E79" s="2">
-        <v>0.0001216299</v>
+        <v>0.0001204636</v>
       </c>
     </row>
     <row r="80">
@@ -1527,16 +1527,16 @@
         <v>11.5</v>
       </c>
       <c r="B80" s="2">
-        <v>6.817003E-05</v>
+        <v>6.215928E-05</v>
       </c>
       <c r="C80" s="2">
-        <v>6.837468E-05</v>
+        <v>6.233963E-05</v>
       </c>
       <c r="D80" s="2">
-        <v>8.09669E-06</v>
+        <v>6.927027E-06</v>
       </c>
       <c r="E80" s="2">
-        <v>0.0001211403</v>
+        <v>0.0001199451</v>
       </c>
     </row>
     <row r="81">
@@ -1544,16 +1544,16 @@
         <v>11.75</v>
       </c>
       <c r="B81" s="2">
-        <v>6.790802E-05</v>
+        <v>6.190409E-05</v>
       </c>
       <c r="C81" s="2">
-        <v>6.811295E-05</v>
+        <v>6.208752E-05</v>
       </c>
       <c r="D81" s="2">
-        <v>8.175803E-06</v>
+        <v>6.99241E-06</v>
       </c>
       <c r="E81" s="2">
-        <v>0.0001206686</v>
+        <v>0.0001194496</v>
       </c>
     </row>
     <row r="82">
@@ -1561,16 +1561,16 @@
         <v>12</v>
       </c>
       <c r="B82" s="2">
-        <v>6.765573E-05</v>
+        <v>6.165991E-05</v>
       </c>
       <c r="C82" s="2">
-        <v>6.786044E-05</v>
+        <v>6.184569E-05</v>
       </c>
       <c r="D82" s="2">
-        <v>8.25459E-06</v>
+        <v>7.057519E-06</v>
       </c>
       <c r="E82" s="2">
-        <v>0.000120214</v>
+        <v>0.0001189749</v>
       </c>
     </row>
     <row r="83">
@@ -1578,16 +1578,16 @@
         <v>12.25</v>
       </c>
       <c r="B83" s="2">
-        <v>6.741277E-05</v>
+        <v>6.142571E-05</v>
       </c>
       <c r="C83" s="2">
-        <v>6.761683E-05</v>
+        <v>6.16132E-05</v>
       </c>
       <c r="D83" s="2">
-        <v>8.333059E-06</v>
+        <v>7.122363E-06</v>
       </c>
       <c r="E83" s="2">
-        <v>0.000119776</v>
+        <v>0.0001185192</v>
       </c>
     </row>
     <row r="84">
@@ -1595,16 +1595,16 @@
         <v>12.5</v>
       </c>
       <c r="B84" s="2">
-        <v>6.717736E-05</v>
+        <v>6.120055E-05</v>
       </c>
       <c r="C84" s="2">
-        <v>6.738047E-05</v>
+        <v>6.138921E-05</v>
       </c>
       <c r="D84" s="2">
-        <v>8.411223E-06</v>
+        <v>7.18695E-06</v>
       </c>
       <c r="E84" s="2">
-        <v>0.0001193513</v>
+        <v>0.0001180806</v>
       </c>
     </row>
     <row r="85">
@@ -1612,16 +1612,16 @@
         <v>12.75</v>
       </c>
       <c r="B85" s="2">
-        <v>6.694911E-05</v>
+        <v>6.098364E-05</v>
       </c>
       <c r="C85" s="2">
-        <v>6.715101E-05</v>
+        <v>6.117301E-05</v>
       </c>
       <c r="D85" s="2">
-        <v>8.489088E-06</v>
+        <v>7.251288E-06</v>
       </c>
       <c r="E85" s="2">
-        <v>0.0001189392</v>
+        <v>0.0001176576</v>
       </c>
     </row>
     <row r="86">
@@ -1629,16 +1629,16 @@
         <v>13</v>
       </c>
       <c r="B86" s="2">
-        <v>6.672817E-05</v>
+        <v>6.077427E-05</v>
       </c>
       <c r="C86" s="2">
-        <v>6.692859E-05</v>
+        <v>6.096394E-05</v>
       </c>
       <c r="D86" s="2">
-        <v>8.56666E-06</v>
+        <v>7.315385E-06</v>
       </c>
       <c r="E86" s="2">
-        <v>0.0001185401</v>
+        <v>0.0001172491</v>
       </c>
     </row>
     <row r="87">
@@ -1646,16 +1646,16 @@
         <v>13.25</v>
       </c>
       <c r="B87" s="2">
-        <v>6.651452E-05</v>
+        <v>6.057187E-05</v>
       </c>
       <c r="C87" s="2">
-        <v>6.671318E-05</v>
+        <v>6.07615E-05</v>
       </c>
       <c r="D87" s="2">
-        <v>8.643943E-06</v>
+        <v>7.379246E-06</v>
       </c>
       <c r="E87" s="2">
-        <v>0.000118154</v>
+        <v>0.0001168538</v>
       </c>
     </row>
     <row r="88">
@@ -1663,16 +1663,16 @@
         <v>13.5</v>
       </c>
       <c r="B88" s="2">
-        <v>6.630673E-05</v>
+        <v>6.037587E-05</v>
       </c>
       <c r="C88" s="2">
-        <v>6.65035E-05</v>
+        <v>6.056515E-05</v>
       </c>
       <c r="D88" s="2">
-        <v>8.720949E-06</v>
+        <v>7.442878E-06</v>
       </c>
       <c r="E88" s="2">
-        <v>0.0001177783</v>
+        <v>0.0001164707</v>
       </c>
     </row>
     <row r="89">
@@ -1680,16 +1680,16 @@
         <v>13.75</v>
       </c>
       <c r="B89" s="2">
-        <v>6.610483E-05</v>
+        <v>6.018573E-05</v>
       </c>
       <c r="C89" s="2">
-        <v>6.629952E-05</v>
+        <v>6.037442E-05</v>
       </c>
       <c r="D89" s="2">
-        <v>8.797681E-06</v>
+        <v>7.506288E-06</v>
       </c>
       <c r="E89" s="2">
-        <v>0.0001174131</v>
+        <v>0.0001160988</v>
       </c>
     </row>
     <row r="90">
@@ -1697,16 +1697,16 @@
         <v>14</v>
       </c>
       <c r="B90" s="2">
-        <v>6.590836E-05</v>
+        <v>6.000104E-05</v>
       </c>
       <c r="C90" s="2">
-        <v>6.610085E-05</v>
+        <v>6.018893E-05</v>
       </c>
       <c r="D90" s="2">
-        <v>8.874148E-06</v>
+        <v>7.56948E-06</v>
       </c>
       <c r="E90" s="2">
-        <v>0.0001170574</v>
+        <v>0.0001157374</v>
       </c>
     </row>
     <row r="91">
@@ -1714,16 +1714,16 @@
         <v>14.25</v>
       </c>
       <c r="B91" s="2">
-        <v>6.571689E-05</v>
+        <v>5.982152E-05</v>
       </c>
       <c r="C91" s="2">
-        <v>6.59071E-05</v>
+        <v>6.000842E-05</v>
       </c>
       <c r="D91" s="2">
-        <v>8.950355E-06</v>
+        <v>7.63246E-06</v>
       </c>
       <c r="E91" s="2">
-        <v>0.0001167107</v>
+        <v>0.0001153859</v>
       </c>
     </row>
     <row r="92">
@@ -1731,16 +1731,16 @@
         <v>14.5</v>
       </c>
       <c r="B92" s="2">
-        <v>6.553E-05</v>
+        <v>5.964669E-05</v>
       </c>
       <c r="C92" s="2">
-        <v>6.571786E-05</v>
+        <v>5.983246E-05</v>
       </c>
       <c r="D92" s="2">
-        <v>9.026307E-06</v>
+        <v>7.695231E-06</v>
       </c>
       <c r="E92" s="2">
-        <v>0.0001163722</v>
+        <v>0.0001150434</v>
       </c>
     </row>
     <row r="93">
@@ -1748,16 +1748,16 @@
         <v>14.75</v>
       </c>
       <c r="B93" s="2">
-        <v>6.534756E-05</v>
+        <v>5.947622E-05</v>
       </c>
       <c r="C93" s="2">
-        <v>6.553302E-05</v>
+        <v>5.966073E-05</v>
       </c>
       <c r="D93" s="2">
-        <v>9.102012E-06</v>
+        <v>7.757801E-06</v>
       </c>
       <c r="E93" s="2">
-        <v>0.0001160415</v>
+        <v>0.0001147093</v>
       </c>
     </row>
     <row r="94">
@@ -1765,16 +1765,16 @@
         <v>15</v>
       </c>
       <c r="B94" s="2">
-        <v>6.516928E-05</v>
+        <v>5.931002E-05</v>
       </c>
       <c r="C94" s="2">
-        <v>6.535232E-05</v>
+        <v>5.949316E-05</v>
       </c>
       <c r="D94" s="2">
-        <v>9.177473E-06</v>
+        <v>7.820171E-06</v>
       </c>
       <c r="E94" s="2">
-        <v>0.0001157183</v>
+        <v>0.0001143834</v>
       </c>
     </row>
     <row r="95">
@@ -1782,16 +1782,16 @@
         <v>15.25</v>
       </c>
       <c r="B95" s="2">
-        <v>6.499497E-05</v>
+        <v>5.914774E-05</v>
       </c>
       <c r="C95" s="2">
-        <v>6.517558E-05</v>
+        <v>5.932943E-05</v>
       </c>
       <c r="D95" s="2">
-        <v>9.252696E-06</v>
+        <v>7.882347E-06</v>
       </c>
       <c r="E95" s="2">
-        <v>0.0001154023</v>
+        <v>0.0001140652</v>
       </c>
     </row>
     <row r="96">
@@ -1799,16 +1799,16 @@
         <v>15.5</v>
       </c>
       <c r="B96" s="2">
-        <v>6.48245E-05</v>
+        <v>5.898913E-05</v>
       </c>
       <c r="C96" s="2">
-        <v>6.500266E-05</v>
+        <v>5.91693E-05</v>
       </c>
       <c r="D96" s="2">
-        <v>9.327685E-06</v>
+        <v>7.944333E-06</v>
       </c>
       <c r="E96" s="2">
-        <v>0.0001150931</v>
+        <v>0.000113754</v>
       </c>
     </row>
     <row r="97">
@@ -1816,16 +1816,16 @@
         <v>15.75</v>
       </c>
       <c r="B97" s="2">
-        <v>6.465775E-05</v>
+        <v>5.883411E-05</v>
       </c>
       <c r="C97" s="2">
-        <v>6.483348E-05</v>
+        <v>5.90127E-05</v>
       </c>
       <c r="D97" s="2">
-        <v>9.402444E-06</v>
+        <v>8.006131E-06</v>
       </c>
       <c r="E97" s="2">
-        <v>0.0001147907</v>
+        <v>0.0001134497</v>
       </c>
     </row>
     <row r="98">
@@ -1833,16 +1833,16 @@
         <v>16</v>
       </c>
       <c r="B98" s="2">
-        <v>6.449451E-05</v>
+        <v>5.868247E-05</v>
       </c>
       <c r="C98" s="2">
-        <v>6.466782E-05</v>
+        <v>5.885944E-05</v>
       </c>
       <c r="D98" s="2">
-        <v>9.476979E-06</v>
+        <v>8.067746E-06</v>
       </c>
       <c r="E98" s="2">
-        <v>0.0001144946</v>
+        <v>0.000113152</v>
       </c>
     </row>
     <row r="99">
@@ -1850,16 +1850,16 @@
         <v>16.25</v>
       </c>
       <c r="B99" s="2">
-        <v>6.433466E-05</v>
+        <v>5.853408E-05</v>
       </c>
       <c r="C99" s="2">
-        <v>6.450555E-05</v>
+        <v>5.87094E-05</v>
       </c>
       <c r="D99" s="2">
-        <v>9.551293E-06</v>
+        <v>8.129182E-06</v>
       </c>
       <c r="E99" s="2">
-        <v>0.0001142046</v>
+        <v>0.0001128606</v>
       </c>
     </row>
     <row r="100">
@@ -1867,16 +1867,16 @@
         <v>16.5</v>
       </c>
       <c r="B100" s="2">
-        <v>6.417818E-05</v>
+        <v>5.838881E-05</v>
       </c>
       <c r="C100" s="2">
-        <v>6.434668E-05</v>
+        <v>5.856244E-05</v>
       </c>
       <c r="D100" s="2">
-        <v>9.625391E-06</v>
+        <v>8.190441E-06</v>
       </c>
       <c r="E100" s="2">
-        <v>0.0001139207</v>
+        <v>0.0001125753</v>
       </c>
     </row>
     <row r="101">
@@ -1884,16 +1884,16 @@
         <v>16.75</v>
       </c>
       <c r="B101" s="2">
-        <v>6.402509E-05</v>
+        <v>5.824654E-05</v>
       </c>
       <c r="C101" s="2">
-        <v>6.41912E-05</v>
+        <v>5.841847E-05</v>
       </c>
       <c r="D101" s="2">
-        <v>9.699274E-06</v>
+        <v>8.251526E-06</v>
       </c>
       <c r="E101" s="2">
-        <v>0.0001136429</v>
+        <v>0.0001122959</v>
       </c>
     </row>
     <row r="102">
@@ -1901,16 +1901,16 @@
         <v>17</v>
       </c>
       <c r="B102" s="2">
-        <v>6.387508E-05</v>
+        <v>5.810718E-05</v>
       </c>
       <c r="C102" s="2">
-        <v>6.403883E-05</v>
+        <v>5.827739E-05</v>
       </c>
       <c r="D102" s="2">
-        <v>9.772949E-06</v>
+        <v>8.312441E-06</v>
       </c>
       <c r="E102" s="2">
-        <v>0.0001133707</v>
+        <v>0.000112022</v>
       </c>
     </row>
     <row r="103">
@@ -1918,16 +1918,16 @@
         <v>17.25</v>
       </c>
       <c r="B103" s="2">
-        <v>6.372808E-05</v>
+        <v>5.797063E-05</v>
       </c>
       <c r="C103" s="2">
-        <v>6.388949E-05</v>
+        <v>5.81391E-05</v>
       </c>
       <c r="D103" s="2">
-        <v>9.846419E-06</v>
+        <v>8.373189E-06</v>
       </c>
       <c r="E103" s="2">
-        <v>0.0001131039</v>
+        <v>0.0001117537</v>
       </c>
     </row>
     <row r="104">
@@ -1935,16 +1935,16 @@
         <v>17.5</v>
       </c>
       <c r="B104" s="2">
-        <v>6.358414E-05</v>
+        <v>5.783681E-05</v>
       </c>
       <c r="C104" s="2">
-        <v>6.374324E-05</v>
+        <v>5.800353E-05</v>
       </c>
       <c r="D104" s="2">
-        <v>9.919686E-06</v>
+        <v>8.433773E-06</v>
       </c>
       <c r="E104" s="2">
-        <v>0.0001128427</v>
+        <v>0.0001114906</v>
       </c>
     </row>
     <row r="105">
@@ -1952,16 +1952,16 @@
         <v>17.75</v>
       </c>
       <c r="B105" s="2">
-        <v>6.344325E-05</v>
+        <v>5.770561E-05</v>
       </c>
       <c r="C105" s="2">
-        <v>6.360005E-05</v>
+        <v>5.787058E-05</v>
       </c>
       <c r="D105" s="2">
-        <v>9.992755E-06</v>
+        <v>8.494194E-06</v>
       </c>
       <c r="E105" s="2">
-        <v>0.0001125869</v>
+        <v>0.0001112327</v>
       </c>
     </row>
     <row r="106">
@@ -1969,16 +1969,16 @@
         <v>18</v>
       </c>
       <c r="B106" s="2">
-        <v>6.330519E-05</v>
+        <v>5.757694E-05</v>
       </c>
       <c r="C106" s="2">
-        <v>6.345972E-05</v>
+        <v>5.774017E-05</v>
       </c>
       <c r="D106" s="2">
-        <v>1.006563E-05</v>
+        <v>8.554456E-06</v>
       </c>
       <c r="E106" s="2">
-        <v>0.0001123363</v>
+        <v>0.0001109797</v>
       </c>
     </row>
     <row r="107">
@@ -1986,16 +1986,16 @@
         <v>18.25</v>
       </c>
       <c r="B107" s="2">
-        <v>6.316987E-05</v>
+        <v>5.745072E-05</v>
       </c>
       <c r="C107" s="2">
-        <v>6.332214E-05</v>
+        <v>5.761221E-05</v>
       </c>
       <c r="D107" s="2">
-        <v>1.013831E-05</v>
+        <v>8.614563E-06</v>
       </c>
       <c r="E107" s="2">
-        <v>0.0001120906</v>
+        <v>0.0001107315</v>
       </c>
     </row>
     <row r="108">
@@ -2003,16 +2003,16 @@
         <v>18.5</v>
       </c>
       <c r="B108" s="2">
-        <v>6.30373E-05</v>
+        <v>5.732694E-05</v>
       </c>
       <c r="C108" s="2">
-        <v>6.318735E-05</v>
+        <v>5.748669E-05</v>
       </c>
       <c r="D108" s="2">
-        <v>1.02108E-05</v>
+        <v>8.674515E-06</v>
       </c>
       <c r="E108" s="2">
-        <v>0.0001118498</v>
+        <v>0.0001104881</v>
       </c>
     </row>
     <row r="109">
@@ -2020,16 +2020,16 @@
         <v>18.75</v>
       </c>
       <c r="B109" s="2">
-        <v>6.290743E-05</v>
+        <v>5.720548E-05</v>
       </c>
       <c r="C109" s="2">
-        <v>6.305527E-05</v>
+        <v>5.736351E-05</v>
       </c>
       <c r="D109" s="2">
-        <v>1.028311E-05</v>
+        <v>8.734317E-06</v>
       </c>
       <c r="E109" s="2">
-        <v>0.000111614</v>
+        <v>0.0001102492</v>
       </c>
     </row>
     <row r="110">
@@ -2037,16 +2037,16 @@
         <v>19</v>
       </c>
       <c r="B110" s="2">
-        <v>6.278013E-05</v>
+        <v>5.708625E-05</v>
       </c>
       <c r="C110" s="2">
-        <v>6.292581E-05</v>
+        <v>5.724257E-05</v>
       </c>
       <c r="D110" s="2">
-        <v>1.035524E-05</v>
+        <v>8.79397E-06</v>
       </c>
       <c r="E110" s="2">
-        <v>0.0001113828</v>
+        <v>0.0001100146</v>
       </c>
     </row>
     <row r="111">
@@ -2054,16 +2054,16 @@
         <v>19.25</v>
       </c>
       <c r="B111" s="2">
-        <v>6.265534E-05</v>
+        <v>5.696921E-05</v>
       </c>
       <c r="C111" s="2">
-        <v>6.279888E-05</v>
+        <v>5.712383E-05</v>
       </c>
       <c r="D111" s="2">
-        <v>1.042719E-05</v>
+        <v>8.853477E-06</v>
       </c>
       <c r="E111" s="2">
-        <v>0.0001111562</v>
+        <v>0.0001097844</v>
       </c>
     </row>
     <row r="112">
@@ -2071,16 +2071,16 @@
         <v>19.5</v>
       </c>
       <c r="B112" s="2">
-        <v>6.253302E-05</v>
+        <v>5.685434E-05</v>
       </c>
       <c r="C112" s="2">
-        <v>6.267445E-05</v>
+        <v>5.700728E-05</v>
       </c>
       <c r="D112" s="2">
-        <v>1.049896E-05</v>
+        <v>8.912841E-06</v>
       </c>
       <c r="E112" s="2">
-        <v>0.000110934</v>
+        <v>0.0001095584</v>
       </c>
     </row>
     <row r="113">
@@ -2088,16 +2088,16 @@
         <v>19.75</v>
       </c>
       <c r="B113" s="2">
-        <v>6.241309E-05</v>
+        <v>5.674158E-05</v>
       </c>
       <c r="C113" s="2">
-        <v>6.255244E-05</v>
+        <v>5.689284E-05</v>
       </c>
       <c r="D113" s="2">
-        <v>1.057056E-05</v>
+        <v>8.972062E-06</v>
       </c>
       <c r="E113" s="2">
-        <v>0.0001107161</v>
+        <v>0.0001093365</v>
       </c>
     </row>
     <row r="114">
@@ -2105,16 +2105,16 @@
         <v>20</v>
       </c>
       <c r="B114" s="2">
-        <v>6.22955E-05</v>
+        <v>5.663085E-05</v>
       </c>
       <c r="C114" s="2">
-        <v>6.243281E-05</v>
+        <v>5.678046E-05</v>
       </c>
       <c r="D114" s="2">
-        <v>1.064199E-05</v>
+        <v>9.031145E-06</v>
       </c>
       <c r="E114" s="2">
-        <v>0.0001105025</v>
+        <v>0.0001091186</v>
       </c>
     </row>
     <row r="115">
@@ -2122,16 +2122,16 @@
         <v>20.25</v>
       </c>
       <c r="B115" s="2">
-        <v>6.218021E-05</v>
+        <v>5.652212E-05</v>
       </c>
       <c r="C115" s="2">
-        <v>6.231549E-05</v>
+        <v>5.66701E-05</v>
       </c>
       <c r="D115" s="2">
-        <v>1.071326E-05</v>
+        <v>9.090091E-06</v>
       </c>
       <c r="E115" s="2">
-        <v>0.0001102931</v>
+        <v>0.0001089046</v>
       </c>
     </row>
     <row r="116">
@@ -2139,16 +2139,16 @@
         <v>20.5</v>
       </c>
       <c r="B116" s="2">
-        <v>6.206714E-05</v>
+        <v>5.641537E-05</v>
       </c>
       <c r="C116" s="2">
-        <v>6.220044E-05</v>
+        <v>5.656173E-05</v>
       </c>
       <c r="D116" s="2">
-        <v>1.078436E-05</v>
+        <v>9.148903E-06</v>
       </c>
       <c r="E116" s="2">
-        <v>0.0001100876</v>
+        <v>0.0001086945</v>
       </c>
     </row>
     <row r="117">
@@ -2156,16 +2156,16 @@
         <v>20.75</v>
       </c>
       <c r="B117" s="2">
-        <v>6.195626E-05</v>
+        <v>5.631056E-05</v>
       </c>
       <c r="C117" s="2">
-        <v>6.208759E-05</v>
+        <v>5.645532E-05</v>
       </c>
       <c r="D117" s="2">
-        <v>1.085529E-05</v>
+        <v>9.207581E-06</v>
       </c>
       <c r="E117" s="2">
-        <v>0.0001098862</v>
+        <v>0.0001084882</v>
       </c>
     </row>
     <row r="118">
@@ -2173,16 +2173,16 @@
         <v>21</v>
       </c>
       <c r="B118" s="2">
-        <v>6.18475E-05</v>
+        <v>5.620765E-05</v>
       </c>
       <c r="C118" s="2">
-        <v>6.197692E-05</v>
+        <v>5.635082E-05</v>
       </c>
       <c r="D118" s="2">
-        <v>1.092607E-05</v>
+        <v>9.266128E-06</v>
       </c>
       <c r="E118" s="2">
-        <v>0.0001096886</v>
+        <v>0.0001082856</v>
       </c>
     </row>
     <row r="119">
@@ -2190,16 +2190,16 @@
         <v>21.25</v>
       </c>
       <c r="B119" s="2">
-        <v>6.174084E-05</v>
+        <v>5.610661E-05</v>
       </c>
       <c r="C119" s="2">
-        <v>6.186837E-05</v>
+        <v>5.624821E-05</v>
       </c>
       <c r="D119" s="2">
-        <v>1.09967E-05</v>
+        <v>9.324548E-06</v>
       </c>
       <c r="E119" s="2">
-        <v>0.0001094948</v>
+        <v>0.0001080867</v>
       </c>
     </row>
     <row r="120">
@@ -2207,16 +2207,16 @@
         <v>21.5</v>
       </c>
       <c r="B120" s="2">
-        <v>6.163624E-05</v>
+        <v>5.600738E-05</v>
       </c>
       <c r="C120" s="2">
-        <v>6.17619E-05</v>
+        <v>5.614743E-05</v>
       </c>
       <c r="D120" s="2">
-        <v>1.106717E-05</v>
+        <v>9.38284E-06</v>
       </c>
       <c r="E120" s="2">
-        <v>0.0001093047</v>
+        <v>0.0001078913</v>
       </c>
     </row>
     <row r="121">
@@ -2224,16 +2224,16 @@
         <v>21.75</v>
       </c>
       <c r="B121" s="2">
-        <v>6.153365E-05</v>
+        <v>5.590995E-05</v>
       </c>
       <c r="C121" s="2">
-        <v>6.165748E-05</v>
+        <v>5.604846E-05</v>
       </c>
       <c r="D121" s="2">
-        <v>1.113748E-05</v>
+        <v>9.441008E-06</v>
       </c>
       <c r="E121" s="2">
-        <v>0.0001091182</v>
+        <v>0.0001076995</v>
       </c>
     </row>
     <row r="122">
@@ -2241,16 +2241,16 @@
         <v>22</v>
       </c>
       <c r="B122" s="2">
-        <v>6.143301E-05</v>
+        <v>5.581427E-05</v>
       </c>
       <c r="C122" s="2">
-        <v>6.155505E-05</v>
+        <v>5.595126E-05</v>
       </c>
       <c r="D122" s="2">
-        <v>1.120766E-05</v>
+        <v>9.499054E-06</v>
       </c>
       <c r="E122" s="2">
-        <v>0.0001089354</v>
+        <v>0.000107511</v>
       </c>
     </row>
     <row r="123">
@@ -2258,16 +2258,16 @@
         <v>22.25</v>
       </c>
       <c r="B123" s="2">
-        <v>6.133431E-05</v>
+        <v>5.572031E-05</v>
       </c>
       <c r="C123" s="2">
-        <v>6.145457E-05</v>
+        <v>5.585579E-05</v>
       </c>
       <c r="D123" s="2">
-        <v>1.127768E-05</v>
+        <v>9.556978E-06</v>
       </c>
       <c r="E123" s="2">
-        <v>0.000108756</v>
+        <v>0.000107326</v>
       </c>
     </row>
     <row r="124">
@@ -2275,16 +2275,16 @@
         <v>22.5</v>
       </c>
       <c r="B124" s="2">
-        <v>6.123751E-05</v>
+        <v>5.562802E-05</v>
       </c>
       <c r="C124" s="2">
-        <v>6.135602E-05</v>
+        <v>5.576202E-05</v>
       </c>
       <c r="D124" s="2">
-        <v>1.134756E-05</v>
+        <v>9.614783E-06</v>
       </c>
       <c r="E124" s="2">
-        <v>0.00010858</v>
+        <v>0.0001071442</v>
       </c>
     </row>
     <row r="125">
@@ -2292,16 +2292,16 @@
         <v>22.75</v>
       </c>
       <c r="B125" s="2">
-        <v>6.114256E-05</v>
+        <v>5.553738E-05</v>
       </c>
       <c r="C125" s="2">
-        <v>6.125936E-05</v>
+        <v>5.566991E-05</v>
       </c>
       <c r="D125" s="2">
-        <v>1.14173E-05</v>
+        <v>9.672471E-06</v>
       </c>
       <c r="E125" s="2">
-        <v>0.0001084075</v>
+        <v>0.0001069657</v>
       </c>
     </row>
     <row r="126">
@@ -2309,16 +2309,16 @@
         <v>23</v>
       </c>
       <c r="B126" s="2">
-        <v>6.104944E-05</v>
+        <v>5.544833E-05</v>
       </c>
       <c r="C126" s="2">
-        <v>6.116454E-05</v>
+        <v>5.55794E-05</v>
       </c>
       <c r="D126" s="2">
-        <v>1.14869E-05</v>
+        <v>9.730044E-06</v>
       </c>
       <c r="E126" s="2">
-        <v>0.0001082382</v>
+        <v>0.0001067903</v>
       </c>
     </row>
     <row r="127">
@@ -2326,16 +2326,16 @@
         <v>23.25</v>
       </c>
       <c r="B127" s="2">
-        <v>6.095809E-05</v>
+        <v>5.536083E-05</v>
       </c>
       <c r="C127" s="2">
-        <v>6.107153E-05</v>
+        <v>5.549048E-05</v>
       </c>
       <c r="D127" s="2">
-        <v>1.155636E-05</v>
+        <v>9.787504E-06</v>
       </c>
       <c r="E127" s="2">
-        <v>0.0001080721</v>
+        <v>0.0001066179</v>
       </c>
     </row>
     <row r="128">
@@ -2343,16 +2343,16 @@
         <v>23.5</v>
       </c>
       <c r="B128" s="2">
-        <v>6.086849E-05</v>
+        <v>5.527489E-05</v>
       </c>
       <c r="C128" s="2">
-        <v>6.098029E-05</v>
+        <v>5.540312E-05</v>
       </c>
       <c r="D128" s="2">
-        <v>1.162569E-05</v>
+        <v>9.844851E-06</v>
       </c>
       <c r="E128" s="2">
-        <v>0.0001079092</v>
+        <v>0.0001064486</v>
       </c>
     </row>
     <row r="129">
@@ -2360,16 +2360,16 @@
         <v>23.75</v>
       </c>
       <c r="B129" s="2">
-        <v>6.078061E-05</v>
+        <v>5.519045E-05</v>
       </c>
       <c r="C129" s="2">
-        <v>6.089079E-05</v>
+        <v>5.531729E-05</v>
       </c>
       <c r="D129" s="2">
-        <v>1.169488E-05</v>
+        <v>9.902088E-06</v>
       </c>
       <c r="E129" s="2">
-        <v>0.0001077495</v>
+        <v>0.0001062822</v>
       </c>
     </row>
     <row r="130">
@@ -2377,16 +2377,16 @@
         <v>24</v>
       </c>
       <c r="B130" s="2">
-        <v>6.06944E-05</v>
+        <v>5.510748E-05</v>
       </c>
       <c r="C130" s="2">
-        <v>6.0803E-05</v>
+        <v>5.523294E-05</v>
       </c>
       <c r="D130" s="2">
-        <v>1.176394E-05</v>
+        <v>9.959217E-06</v>
       </c>
       <c r="E130" s="2">
-        <v>0.0001075927</v>
+        <v>0.0001061187</v>
       </c>
     </row>
   </sheetData>
@@ -2400,7 +2400,7 @@
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.85" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.05" bestFit="1" customWidth="1"/>
   </cols>
@@ -2427,7 +2427,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="2">
-        <v>3704.58769798279</v>
+        <v>3870.3773021698</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
@@ -2441,7 +2441,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="2">
-        <v>3957.60679244995</v>
+        <v>4167.89722442627</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>11</v>
@@ -2455,7 +2455,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="2">
-        <v>0.374472321709618</v>
+        <v>0.41803898056969</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -2469,7 +2469,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="2">
-        <v>6081.85172702598</v>
+        <v>6633.56431237184</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -2486,10 +2486,10 @@
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="107.7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="98.7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="98.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="118.65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2514,16 +2514,16 @@
         <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>0.77263480424881</v>
+        <v>0.673915386199951</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>1.36919093132019</v>
+        <v>1.29800271987915</v>
       </c>
       <c r="E2" s="2">
-        <v>0.785820603370667</v>
+        <v>0.684157013893127</v>
       </c>
     </row>
     <row r="3">
@@ -2531,16 +2531,16 @@
         <v>21</v>
       </c>
       <c r="B3" s="2">
-        <v>2625615478515.63</v>
+        <v>2356312011718.75</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>4652869628906.25</v>
+        <v>4538402832031.25</v>
       </c>
       <c r="E3" s="2">
-        <v>2670424316406.25</v>
+        <v>2392121582031.25</v>
       </c>
     </row>
     <row r="4">
@@ -2548,16 +2548,16 @@
         <v>22</v>
       </c>
       <c r="B4" s="2">
-        <v>0.140512511134148</v>
+        <v>0.1309754550457</v>
       </c>
       <c r="C4" s="2">
-        <v>0.0115364724770188</v>
+        <v>0.0098585095256567</v>
       </c>
       <c r="D4" s="2">
-        <v>0.260482609272003</v>
+        <v>0.263966649770737</v>
       </c>
       <c r="E4" s="2">
-        <v>0.144372463226318</v>
+        <v>0.134729012846947</v>
       </c>
     </row>
     <row r="5">
@@ -2565,16 +2565,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="2">
-        <v>477498291015.625</v>
+        <v>457949249267.578</v>
       </c>
       <c r="C5" s="2">
-        <v>39203956604.0039</v>
+        <v>34469795227.0508</v>
       </c>
       <c r="D5" s="2">
-        <v>885188171386.719</v>
+        <v>922946472167.969</v>
       </c>
       <c r="E5" s="2">
-        <v>490615447998.047</v>
+        <v>471073394775.391</v>
       </c>
     </row>
     <row r="6">
@@ -2582,16 +2582,16 @@
         <v>24</v>
       </c>
       <c r="B6" s="2">
-        <v>0.00120398204308003</v>
+        <v>0.00116683600936085</v>
       </c>
       <c r="C6" s="2">
-        <v>1.17639428935945E-05</v>
+        <v>9.95921709545655E-06</v>
       </c>
       <c r="D6" s="2">
-        <v>0.00193831091746688</v>
+        <v>0.00191633054055274</v>
       </c>
       <c r="E6" s="2">
-        <v>0.00153267232235521</v>
+        <v>0.00149069831240922</v>
       </c>
     </row>
     <row r="7">
@@ -2599,16 +2599,16 @@
         <v>25</v>
       </c>
       <c r="B7" s="2">
-        <v>4091446.39968872</v>
+        <v>4079784.87014771</v>
       </c>
       <c r="C7" s="2">
-        <v>39976.9619107246</v>
+        <v>34821.9163715839</v>
       </c>
       <c r="D7" s="2">
-        <v>6586888.31329346</v>
+        <v>6700356.00662231</v>
       </c>
       <c r="E7" s="2">
-        <v>5208422.18399048</v>
+        <v>5212153.43475342</v>
       </c>
     </row>
     <row r="8">
@@ -2616,16 +2616,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="2">
-        <v>6.08029986324254E-05</v>
+        <v>5.52329438505694E-05</v>
       </c>
       <c r="C8" s="2">
-        <v>1.17639428935945E-05</v>
+        <v>9.95921709545655E-06</v>
       </c>
       <c r="D8" s="2">
-        <v>0.000107592743006535</v>
+        <v>0.000106118721305393</v>
       </c>
       <c r="E8" s="2">
-        <v>6.06944013270549E-05</v>
+        <v>5.51074808754493E-05</v>
       </c>
     </row>
     <row r="9">
@@ -2633,16 +2633,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="2">
-        <v>0.38086308632046</v>
+        <v>0.42439199751243</v>
       </c>
       <c r="C9" s="2" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="D9" s="2">
-        <v>0.214921121369116</v>
+        <v>0.220341826207004</v>
       </c>
       <c r="E9" s="2">
-        <v>0.374472321709618</v>
+        <v>0.41803898056969</v>
       </c>
     </row>
     <row r="10">
@@ -2650,16 +2650,16 @@
         <v>28</v>
       </c>
       <c r="B10" s="2">
-        <v>0.818138539791107</v>
+        <v>0.805649995803833</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D10" s="2">
-        <v>0.809754371643066</v>
+        <v>0.796636283397675</v>
       </c>
       <c r="E10" s="2">
-        <v>0.816278100013733</v>
+        <v>0.803072988986969</v>
       </c>
     </row>
     <row r="11">
@@ -2667,16 +2667,16 @@
         <v>30</v>
       </c>
       <c r="B11" s="2">
-        <v>162.926871744792</v>
+        <v>152.936165364583</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D11" s="2">
-        <v>160.043326822917</v>
+        <v>150.109114583333</v>
       </c>
       <c r="E11" s="2">
-        <v>164.880338541667</v>
+        <v>154.306884765625</v>
       </c>
     </row>
     <row r="12">
@@ -2701,16 +2701,16 @@
         <v>32</v>
       </c>
       <c r="B13" s="2">
-        <v>120.102026367188</v>
+        <v>113.560628255208</v>
       </c>
       <c r="C13" s="2">
-        <v>-29.4301534016927</v>
+        <v>-30.1221130371094</v>
       </c>
       <c r="D13" s="2">
-        <v>119.044287109375</v>
+        <v>112.568758138021</v>
       </c>
       <c r="E13" s="2">
-        <v>122.091975911458</v>
+        <v>115.179305013021</v>
       </c>
     </row>
     <row r="14">
@@ -2718,16 +2718,16 @@
         <v>33</v>
       </c>
       <c r="B14" s="2">
-        <v>3959.5422744751</v>
+        <v>4171.77391052246</v>
       </c>
       <c r="C14" s="2" t="e">
         <v>#DIV/0!</v>
       </c>
       <c r="D14" s="2">
-        <v>2214.69259262085</v>
+        <v>2147.04251289368</v>
       </c>
       <c r="E14" s="2">
-        <v>3957.60679244995</v>
+        <v>4167.89722442627</v>
       </c>
     </row>
     <row r="15">
@@ -2735,16 +2735,16 @@
         <v>34</v>
       </c>
       <c r="B15" s="2">
-        <v>3723.16980361938</v>
+        <v>3894.29330825806</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="2">
-        <v>2063.80152702332</v>
+        <v>1984.51900482178</v>
       </c>
       <c r="E15" s="2">
-        <v>3704.58769798279</v>
+        <v>3870.3773021698</v>
       </c>
     </row>
   </sheetData>
